--- a/data/employees/EMP046/AST-EMP046-06.xlsx
+++ b/data/employees/EMP046/AST-EMP046-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Productivity Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,199 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Shift Productivity Report - Avery Wilson (Operations)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Avery Wilson | Role: Specialist | Location: Bengaluru | Date: 2025-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>97</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Shift</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Efficiency %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>EMP046</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Team Lead A</t>
+          <t>Ast Emp046 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>96</v>
+        <v>93</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>EMP046</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Team Lead B</t>
+          <t>Ast Emp046 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>EMP046</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Team Lead C</t>
+          <t>Ast Emp046 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>Mentoring</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>92</v>
+        <v>64</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>EMP046</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead D</t>
+          <t>Ast Emp046 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G8" t="n">
-        <v>96.8</v>
+        <v>84</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>88</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>74</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>97</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>65</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>70</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>87</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>95</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>61</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>80</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>78</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>97</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>63</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>62</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>90</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp046 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>86</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP046</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP046 contributes to ast emp046 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>